--- a/BILAN LOUMA PHASE1.xlsx
+++ b/BILAN LOUMA PHASE1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>DR</t>
   </si>
@@ -99,13 +99,40 @@
   </si>
   <si>
     <t>TOT OM</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BILAN DES REALISATIONS SIM - JUILLET </t>
+  </si>
+  <si>
+    <t>SEM1</t>
+  </si>
+  <si>
+    <t>SEM2</t>
+  </si>
+  <si>
+    <t>SEM3</t>
+  </si>
+  <si>
+    <t>SEM4</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                   </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,8 +152,43 @@
       <name val="Arial Black"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +204,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47D359"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -179,22 +259,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -203,9 +284,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -483,32 +583,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I23"/>
+  <dimension ref="B1:T23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,198 +627,305 @@
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>1461</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>1654</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>1272</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="2">
+        <v>1402</v>
+      </c>
+      <c r="H4" s="2">
         <v>4387</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="2">
         <v>2880</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="3">
         <v>1.52</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>1017</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>1529</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>1736</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>1009</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>5291</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="2">
         <v>3800</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="3">
         <v>1.39</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>1026</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>1421</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>1533</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>1056</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>5036</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="2">
         <v>3800</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="3">
         <v>1.32</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B7" s="4" t="s">
+      <c r="S6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>513</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>1166</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>1286</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>995</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
         <v>3960</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="2">
         <v>3800</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="3">
         <v>1.04</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>595</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>1182</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>1503</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>1054</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
         <v>4334</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="2">
         <v>3800</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="3">
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>527</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>1057</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>1051</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>731</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
         <v>3366</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="2">
         <v>3800</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="3">
         <v>0.89</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="2:20" ht="21" x14ac:dyDescent="0.5">
+      <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>3678</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>7816</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>8763</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>6117</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
         <v>26374</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="2">
         <v>21880</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="3">
         <v>1.21</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="M10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M11" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="8">
+        <v>569</v>
+      </c>
+      <c r="O12" s="8">
+        <v>299</v>
+      </c>
+      <c r="P12" s="8">
+        <v>301</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>233</v>
+      </c>
+      <c r="R12" s="8">
+        <f t="shared" ref="R12:R18" si="0">SUM(N12:Q12)</f>
+        <v>1402</v>
+      </c>
+      <c r="S12" s="8">
+        <v>960</v>
+      </c>
+      <c r="T12" s="11">
+        <f>R12/S12</f>
+        <v>1.4604166666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="8">
+        <v>230</v>
+      </c>
+      <c r="O13" s="8">
+        <v>225</v>
+      </c>
+      <c r="P13" s="8">
+        <v>240</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>261</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" si="0"/>
+        <v>956</v>
+      </c>
+      <c r="S13" s="8">
+        <v>960</v>
+      </c>
+      <c r="T13" s="11">
+        <f>R13/S13</f>
+        <v>0.99583333333333335</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" s="6" t="s">
         <v>23</v>
       </c>
@@ -727,8 +936,35 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="6"/>
+      <c r="M14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="8">
+        <v>356</v>
+      </c>
+      <c r="O14" s="8">
+        <v>275</v>
+      </c>
+      <c r="P14" s="8">
+        <v>318</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>236</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="0"/>
+        <v>1185</v>
+      </c>
+      <c r="S14" s="8">
+        <v>960</v>
+      </c>
+      <c r="T14" s="11">
+        <f>R14/S14</f>
+        <v>1.234375</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -737,8 +973,35 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J15" s="7"/>
+      <c r="M15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="8">
+        <v>182</v>
+      </c>
+      <c r="O15" s="8">
+        <v>296</v>
+      </c>
+      <c r="P15" s="8">
+        <v>215</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>248</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" si="0"/>
+        <v>941</v>
+      </c>
+      <c r="S15" s="8">
+        <v>960</v>
+      </c>
+      <c r="T15" s="12">
+        <f>+R15/S15</f>
+        <v>0.98020833333333335</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,202 +1017,290 @@
       <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="4" t="s">
+      <c r="M16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="8">
+        <v>287</v>
+      </c>
+      <c r="O16" s="8">
+        <v>313</v>
+      </c>
+      <c r="P16" s="8">
+        <v>304</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>257</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="0"/>
+        <v>1161</v>
+      </c>
+      <c r="S16" s="8">
+        <v>960</v>
+      </c>
+      <c r="T16" s="11">
+        <f>+R16/S16</f>
+        <v>1.2093750000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>0</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>1099</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>200</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>86</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2">
         <v>1385</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="2">
         <v>1440</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="J17" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="4" t="s">
+      <c r="M17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" s="8">
+        <v>238</v>
+      </c>
+      <c r="O17" s="8">
+        <v>255</v>
+      </c>
+      <c r="P17" s="8">
+        <v>209</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>257</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" si="0"/>
+        <v>959</v>
+      </c>
+      <c r="S17" s="8">
+        <v>960</v>
+      </c>
+      <c r="T17" s="11">
+        <f>+R17/S17</f>
+        <v>0.99895833333333328</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>473</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>753</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>349</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>185</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2">
         <v>1760</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="2">
         <v>1920</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="J18" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="4" t="s">
+      <c r="M18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="10">
+        <v>1862</v>
+      </c>
+      <c r="O18" s="10">
+        <v>1663</v>
+      </c>
+      <c r="P18" s="10">
+        <v>1587</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>1492</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="0"/>
+        <v>6604</v>
+      </c>
+      <c r="S18" s="8">
+        <f>SUM(S12:S17)</f>
+        <v>5760</v>
+      </c>
+      <c r="T18" s="13">
+        <f>+R18/S18</f>
+        <v>1.1465277777777778</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>526</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>308</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>220</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>127</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2">
         <v>1181</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="2">
         <v>1920</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>630</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>556</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>131</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>123</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="2"/>
+      <c r="H20" s="2">
         <v>1440</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="2">
         <v>1920</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="J20" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="4" t="s">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>557</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>180</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>10</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>10</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="2"/>
+      <c r="H21" s="2">
         <v>757</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="2">
         <v>1920</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="4" t="s">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>283</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>77</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>3</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>3</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2">
         <v>366</v>
       </c>
-      <c r="H22" s="4">
+      <c r="I22" s="2">
         <v>1920</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="J22" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B23" s="4" t="s">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>2469</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>2973</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
         <v>913</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>534</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2">
         <v>6889</v>
       </c>
-      <c r="H23" s="4">
+      <c r="I23" s="2">
         <v>11040</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="J23" s="3" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:I2"/>
-    <mergeCell ref="B14:I15"/>
+  <mergeCells count="3">
+    <mergeCell ref="B1:J2"/>
+    <mergeCell ref="B14:J15"/>
+    <mergeCell ref="M10:T10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -982,6 +1333,10 @@
               <xm:f>' BILAN LOUMA PHASE1 SIM&amp;OM'!F3:F3</xm:f>
               <xm:sqref>F3</xm:sqref>
             </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>' BILAN LOUMA PHASE1 SIM&amp;OM'!G3:G3</xm:f>
+              <xm:sqref>G3</xm:sqref>
+            </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
       </x14:sparklineGroups>

--- a/BILAN LOUMA PHASE1.xlsx
+++ b/BILAN LOUMA PHASE1.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="7050" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name=" BILAN LOUMA PHASE1 SIM&amp;OM" sheetId="1" r:id="rId1"/>
-    <sheet name="COMMISSIONS" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil2" sheetId="3" r:id="rId3"/>
+    <sheet name="Carburants &amp; Hebergement" sheetId="3" r:id="rId2"/>
+    <sheet name="COMMISSIONS" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$1:$K$10</definedName>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="74">
   <si>
     <t>DR</t>
   </si>
@@ -165,12 +165,99 @@
   <si>
     <t>OM</t>
   </si>
+  <si>
+    <t>Mars et Avril</t>
+  </si>
+  <si>
+    <t>MAI</t>
+  </si>
+  <si>
+    <t>JUIN</t>
+  </si>
+  <si>
+    <t>JUILLET</t>
+  </si>
+  <si>
+    <t>février</t>
+  </si>
+  <si>
+    <t>mars</t>
+  </si>
+  <si>
+    <t>avril</t>
+  </si>
+  <si>
+    <t>mai</t>
+  </si>
+  <si>
+    <t>juin</t>
+  </si>
+  <si>
+    <t>juillet</t>
+  </si>
+  <si>
+    <t>août</t>
+  </si>
+  <si>
+    <t>Quantité.</t>
+  </si>
+  <si>
+    <t>Montant.</t>
+  </si>
+  <si>
+    <t>AA 041 WZ</t>
+  </si>
+  <si>
+    <t>AA 312 WH</t>
+  </si>
+  <si>
+    <t>AA 314 WH</t>
+  </si>
+  <si>
+    <t>AA 321 WH</t>
+  </si>
+  <si>
+    <t>AA 756 WH</t>
+  </si>
+  <si>
+    <t>AA 759 WH</t>
+  </si>
+  <si>
+    <t>Total général</t>
+  </si>
+  <si>
+    <t>Véhicule</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>Montant</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>CARBURANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>SYNTHESE :</t>
+  </si>
+  <si>
+    <t>HEBERGEMENT</t>
+  </si>
+  <si>
+    <t>COMISSIONS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,8 +342,38 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF212121"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,8 +422,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE97132"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -390,12 +543,456 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFF4B084"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFF4B084"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFF4B084"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF4B084"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFF4B084"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF4B084"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -452,6 +1049,90 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -476,12 +1157,70 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3081,7 +3820,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -3367,7 +4105,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$D$3</c15:sqref>
@@ -3458,7 +4196,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -3479,7 +4217,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -3511,7 +4249,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$D$4:$D$9</c15:sqref>
@@ -3542,7 +4280,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -3555,7 +4293,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$E$3</c15:sqref>
@@ -3646,7 +4384,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -3667,7 +4405,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -3699,7 +4437,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$E$4:$E$9</c15:sqref>
@@ -3730,7 +4468,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -3743,7 +4481,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$F$3</c15:sqref>
@@ -3837,7 +4575,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -3858,7 +4596,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -3890,7 +4628,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$F$4:$F$9</c15:sqref>
@@ -3921,7 +4659,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -3934,7 +4672,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$G$3</c15:sqref>
@@ -4028,7 +4766,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -4049,7 +4787,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -4081,7 +4819,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$G$4:$G$9</c15:sqref>
@@ -4112,7 +4850,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -4125,7 +4863,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$H$3</c15:sqref>
@@ -4219,7 +4957,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -4240,7 +4978,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -4272,7 +5010,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$H$4:$H$9</c15:sqref>
@@ -4303,7 +5041,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000005-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -4316,7 +5054,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$I$3</c15:sqref>
@@ -4413,7 +5151,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -4434,7 +5172,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -4466,7 +5204,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$I$4:$I$9</c15:sqref>
@@ -4497,7 +5235,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -4510,7 +5248,7 @@
                 <c:order val="7"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$J$3</c15:sqref>
@@ -4607,7 +5345,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -4628,7 +5366,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$4:$B$9</c15:sqref>
@@ -4660,7 +5398,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$J$4:$J$9</c15:sqref>
@@ -4691,7 +5429,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000007-4E58-4A81-B40F-099B950C4C4E}"/>
                   </c:ext>
@@ -5465,7 +6203,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$D$16</c15:sqref>
@@ -5556,7 +6294,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -5577,7 +6315,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -5609,7 +6347,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$D$17:$D$22</c15:sqref>
@@ -5640,7 +6378,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -5653,7 +6391,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$E$16</c15:sqref>
@@ -5744,7 +6482,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -5765,7 +6503,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -5797,7 +6535,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$E$17:$E$22</c15:sqref>
@@ -5828,7 +6566,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -5841,7 +6579,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$F$16</c15:sqref>
@@ -5935,7 +6673,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -5956,7 +6694,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -5988,7 +6726,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$F$17:$F$22</c15:sqref>
@@ -6019,7 +6757,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -6032,7 +6770,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$G$16</c15:sqref>
@@ -6126,7 +6864,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -6147,7 +6885,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -6179,7 +6917,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$G$17:$G$22</c15:sqref>
@@ -6210,7 +6948,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -6223,7 +6961,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$H$16</c15:sqref>
@@ -6317,7 +7055,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -6338,7 +7076,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -6370,7 +7108,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$H$17:$H$22</c15:sqref>
@@ -6401,7 +7139,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000005-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -6414,7 +7152,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$I$16</c15:sqref>
@@ -6511,7 +7249,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -6532,7 +7270,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -6564,7 +7302,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$I$17:$I$22</c15:sqref>
@@ -6595,7 +7333,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -6608,7 +7346,7 @@
                 <c:order val="7"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$J$16</c15:sqref>
@@ -6705,7 +7443,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -6726,7 +7464,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$B$17:$B$22</c15:sqref>
@@ -6758,7 +7496,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>' BILAN LOUMA PHASE1 SIM&amp;OM'!$J$17:$J$22</c15:sqref>
@@ -6789,7 +7527,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000007-30F6-45AE-83B5-B358B34FCB21}"/>
                   </c:ext>
@@ -9570,30 +10308,30 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="2:21" ht="14.5" customHeight="1">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
     </row>
     <row r="2" spans="2:21" ht="14.5" customHeight="1">
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
     </row>
     <row r="3" spans="2:21">
       <c r="B3" s="1" t="s">
@@ -9870,16 +10608,16 @@
         <f t="shared" si="1"/>
         <v>1.182814371257485</v>
       </c>
-      <c r="N10" s="27" t="s">
+      <c r="N10" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="63"/>
+      <c r="S10" s="63"/>
+      <c r="T10" s="63"/>
+      <c r="U10" s="63"/>
     </row>
     <row r="11" spans="2:21">
       <c r="N11" s="5" t="s">
@@ -9964,18 +10702,18 @@
       </c>
     </row>
     <row r="14" spans="2:21">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
       <c r="N14" s="4" t="s">
         <v>6</v>
       </c>
@@ -10004,16 +10742,16 @@
       </c>
     </row>
     <row r="15" spans="2:21">
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
       <c r="N15" s="4" t="s">
         <v>7</v>
       </c>
@@ -10396,12 +11134,12 @@
     <row r="26" spans="2:21" hidden="1"/>
     <row r="27" spans="2:21" hidden="1"/>
     <row r="29" spans="2:21" ht="18.5" customHeight="1">
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="22"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="58"/>
     </row>
     <row r="30" spans="2:21" ht="18.5">
       <c r="B30" s="17" t="s">
@@ -10543,285 +11281,1028 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="2:16" ht="15" thickBot="1"/>
+    <row r="2" spans="2:16">
+      <c r="E2" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="79"/>
+    </row>
+    <row r="3" spans="2:16" ht="15" thickBot="1">
+      <c r="E3" s="80"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" thickBot="1"/>
+    <row r="5" spans="2:16">
+      <c r="B5" s="25"/>
+      <c r="C5" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="65"/>
+      <c r="E5" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="65"/>
+      <c r="G5" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="65"/>
+      <c r="I5" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="65"/>
+      <c r="K5" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="65"/>
+      <c r="M5" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="65"/>
+      <c r="O5" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="65"/>
+    </row>
+    <row r="6" spans="2:16" ht="15" thickBot="1">
+      <c r="B6" s="26"/>
+      <c r="C6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32">
+        <v>138.66999999999999</v>
+      </c>
+      <c r="F7" s="31">
+        <v>104698</v>
+      </c>
+      <c r="G7" s="32">
+        <v>132.78</v>
+      </c>
+      <c r="H7" s="31">
+        <v>100252</v>
+      </c>
+      <c r="I7" s="32">
+        <v>138.91</v>
+      </c>
+      <c r="J7" s="31">
+        <v>104875</v>
+      </c>
+      <c r="K7" s="32">
+        <v>137.9</v>
+      </c>
+      <c r="L7" s="31">
+        <v>104116</v>
+      </c>
+      <c r="M7" s="32">
+        <v>140.06</v>
+      </c>
+      <c r="N7" s="31">
+        <v>105746</v>
+      </c>
+      <c r="O7" s="32">
+        <v>116.16</v>
+      </c>
+      <c r="P7" s="31">
+        <v>87700</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="B8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="32">
+        <v>199.19</v>
+      </c>
+      <c r="D8" s="31">
+        <v>150380</v>
+      </c>
+      <c r="E8" s="32">
+        <v>299.52999999999997</v>
+      </c>
+      <c r="F8" s="31">
+        <v>226140</v>
+      </c>
+      <c r="G8" s="32">
+        <v>393.96</v>
+      </c>
+      <c r="H8" s="31">
+        <v>297425</v>
+      </c>
+      <c r="I8" s="32">
+        <v>400</v>
+      </c>
+      <c r="J8" s="31">
+        <v>301973</v>
+      </c>
+      <c r="K8" s="32">
+        <v>397.37</v>
+      </c>
+      <c r="L8" s="31">
+        <v>300013</v>
+      </c>
+      <c r="M8" s="32">
+        <v>398.87</v>
+      </c>
+      <c r="N8" s="31">
+        <v>301140</v>
+      </c>
+      <c r="O8" s="32">
+        <v>387.77</v>
+      </c>
+      <c r="P8" s="31">
+        <v>292750</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="32">
+        <v>99.09</v>
+      </c>
+      <c r="D9" s="31">
+        <v>74813</v>
+      </c>
+      <c r="E9" s="32">
+        <v>388.71</v>
+      </c>
+      <c r="F9" s="31">
+        <v>293475</v>
+      </c>
+      <c r="G9" s="32">
+        <v>394.62</v>
+      </c>
+      <c r="H9" s="31">
+        <v>297935</v>
+      </c>
+      <c r="I9" s="32">
+        <v>346.7</v>
+      </c>
+      <c r="J9" s="31">
+        <v>261765</v>
+      </c>
+      <c r="K9" s="32">
+        <v>286.39</v>
+      </c>
+      <c r="L9" s="31">
+        <v>216228</v>
+      </c>
+      <c r="M9" s="32">
+        <v>399.97</v>
+      </c>
+      <c r="N9" s="31">
+        <v>301978</v>
+      </c>
+      <c r="O9" s="32">
+        <v>399.76</v>
+      </c>
+      <c r="P9" s="31">
+        <v>301825</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="32">
+        <v>142.72</v>
+      </c>
+      <c r="D10" s="31">
+        <v>107750</v>
+      </c>
+      <c r="E10" s="32">
+        <v>399.14</v>
+      </c>
+      <c r="F10" s="31">
+        <v>301338</v>
+      </c>
+      <c r="G10" s="32">
+        <v>399.88</v>
+      </c>
+      <c r="H10" s="31">
+        <v>301893</v>
+      </c>
+      <c r="I10" s="32">
+        <v>499.39</v>
+      </c>
+      <c r="J10" s="31">
+        <v>377038</v>
+      </c>
+      <c r="K10" s="32">
+        <v>403</v>
+      </c>
+      <c r="L10" s="31">
+        <v>304265</v>
+      </c>
+      <c r="M10" s="32">
+        <v>499.64</v>
+      </c>
+      <c r="N10" s="31">
+        <v>377228</v>
+      </c>
+      <c r="O10" s="32">
+        <v>500</v>
+      </c>
+      <c r="P10" s="31">
+        <v>377500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="32">
+        <v>161.96</v>
+      </c>
+      <c r="D11" s="31">
+        <v>122280</v>
+      </c>
+      <c r="E11" s="32">
+        <v>397.01</v>
+      </c>
+      <c r="F11" s="31">
+        <v>299747</v>
+      </c>
+      <c r="G11" s="32">
+        <v>399.94</v>
+      </c>
+      <c r="H11" s="31">
+        <v>301947</v>
+      </c>
+      <c r="I11" s="32">
+        <v>299.2</v>
+      </c>
+      <c r="J11" s="31">
+        <v>225902</v>
+      </c>
+      <c r="K11" s="32">
+        <v>233.35</v>
+      </c>
+      <c r="L11" s="31">
+        <v>176181</v>
+      </c>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="31"/>
+    </row>
+    <row r="12" spans="2:16" ht="15" thickBot="1">
+      <c r="B12" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="32">
+        <v>163.72999999999999</v>
+      </c>
+      <c r="D12" s="31">
+        <v>123618</v>
+      </c>
+      <c r="E12" s="32">
+        <v>299.64</v>
+      </c>
+      <c r="F12" s="31">
+        <v>226230</v>
+      </c>
+      <c r="G12" s="32">
+        <v>549.53</v>
+      </c>
+      <c r="H12" s="31">
+        <v>414895</v>
+      </c>
+      <c r="I12" s="32">
+        <v>549.95000000000005</v>
+      </c>
+      <c r="J12" s="31">
+        <v>415218</v>
+      </c>
+      <c r="K12" s="32">
+        <v>490.47</v>
+      </c>
+      <c r="L12" s="31">
+        <v>370306</v>
+      </c>
+      <c r="M12" s="32">
+        <v>549.79</v>
+      </c>
+      <c r="N12" s="31">
+        <v>415095</v>
+      </c>
+      <c r="O12" s="32">
+        <v>549.66</v>
+      </c>
+      <c r="P12" s="31">
+        <v>414985</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="15" thickBot="1">
+      <c r="B13" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="34">
+        <v>766.69</v>
+      </c>
+      <c r="D13" s="35">
+        <v>578841</v>
+      </c>
+      <c r="E13" s="34">
+        <v>1922.7</v>
+      </c>
+      <c r="F13" s="35">
+        <v>1451628</v>
+      </c>
+      <c r="G13" s="34">
+        <v>2270.71</v>
+      </c>
+      <c r="H13" s="35">
+        <v>1714347</v>
+      </c>
+      <c r="I13" s="34">
+        <v>2234.15</v>
+      </c>
+      <c r="J13" s="35">
+        <v>1686771</v>
+      </c>
+      <c r="K13" s="34">
+        <v>1948.48</v>
+      </c>
+      <c r="L13" s="35">
+        <v>1471109</v>
+      </c>
+      <c r="M13" s="34">
+        <v>1988.33</v>
+      </c>
+      <c r="N13" s="35">
+        <v>1501187</v>
+      </c>
+      <c r="O13" s="34">
+        <v>1953.35</v>
+      </c>
+      <c r="P13" s="35">
+        <v>1474760</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" ht="15" thickBot="1"/>
+    <row r="18" spans="4:16" ht="15" thickBot="1">
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="84"/>
+      <c r="G18" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>1</v>
+      <c r="H18" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="67"/>
+      <c r="L18">
+        <f>+SUM(D13+F13+H13+J13+L13)</f>
+        <v>6902696</v>
+      </c>
+      <c r="N18">
+        <f>+SUM(L18+N13+P13)</f>
+        <v>9878643</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42">
-      <c r="A2" s="9" t="s">
+    <row r="19" spans="4:16" ht="15" thickBot="1">
+      <c r="E19" s="83"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="P19">
+        <f>+SUM(N13+P13)</f>
+        <v>2975947</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16">
+      <c r="G20" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="49">
+        <f>+SUM(E7+G7+I7+K7+M7+O7)</f>
+        <v>804.4799999999999</v>
+      </c>
+      <c r="J20" s="47">
+        <f>+SUM(F7+H7+J7+L7+N7+P7)</f>
+        <v>607387</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16">
+      <c r="G21" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="50">
+        <f t="shared" ref="I21:J23" si="0">+SUM(C8+E8+G8+I8+K8+M8+O8)</f>
+        <v>2476.6899999999996</v>
+      </c>
+      <c r="J21" s="46">
+        <f t="shared" si="0"/>
+        <v>1869821</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16">
+      <c r="G22" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="50">
+        <f t="shared" si="0"/>
+        <v>2315.2399999999998</v>
+      </c>
+      <c r="J22" s="45">
+        <f t="shared" si="0"/>
+        <v>1748019</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16">
+      <c r="G23" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="50">
+        <f t="shared" si="0"/>
+        <v>2843.77</v>
+      </c>
+      <c r="J23" s="37">
+        <f t="shared" si="0"/>
+        <v>2147012</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16">
+      <c r="G24" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="13">
-        <v>196875</v>
-      </c>
-      <c r="D2" s="13">
-        <v>645313</v>
-      </c>
-      <c r="E2" s="13">
-        <v>656250</v>
-      </c>
-      <c r="F2" s="14">
-        <v>581875</v>
-      </c>
-      <c r="G2" s="14">
-        <v>578813</v>
-      </c>
-      <c r="H2" s="14">
-        <v>580125</v>
-      </c>
-      <c r="I2" s="14">
-        <v>545125</v>
-      </c>
-      <c r="J2" s="15">
-        <f>+SUM(C2:I2)</f>
-        <v>3784376</v>
+      <c r="H24" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="50">
+        <f>+SUM(C11+E11+G11+I11+K11)</f>
+        <v>1491.46</v>
+      </c>
+      <c r="J24" s="37">
+        <f>+SUM(D11+F11+H11+J11+L11)</f>
+        <v>1126057</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="42">
-      <c r="A3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="13">
-        <v>134313</v>
-      </c>
-      <c r="D3" s="13">
-        <v>518438</v>
-      </c>
-      <c r="E3" s="13">
-        <v>611188</v>
-      </c>
-      <c r="F3" s="14">
-        <v>551688</v>
-      </c>
-      <c r="G3" s="13">
-        <v>478625</v>
-      </c>
-      <c r="H3" s="14">
-        <v>579250</v>
-      </c>
-      <c r="I3" s="14">
-        <v>444063</v>
-      </c>
-      <c r="J3" s="15">
-        <f t="shared" ref="J3:J8" si="0">+SUM(C3:I3)</f>
-        <v>3317565</v>
+    <row r="25" spans="4:16" ht="15" thickBot="1">
+      <c r="G25" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25" s="40">
+        <f>+SUM(C12+E12+G12+I12+K12+M12+O12)</f>
+        <v>3152.7699999999995</v>
+      </c>
+      <c r="J25" s="37">
+        <f>+SUM(D12+F12+H12+J12+L12+N12+P12)</f>
+        <v>2380347</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="42">
-      <c r="A4" s="9" t="s">
+    <row r="26" spans="4:16" ht="15" thickBot="1">
+      <c r="G26" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="69"/>
+      <c r="I26" s="41">
+        <f>+SUM(I20:I25)</f>
+        <v>13084.41</v>
+      </c>
+      <c r="J26" s="41">
+        <f>+SUM(J20:J25)</f>
+        <v>9878643</v>
+      </c>
+    </row>
+    <row r="29" spans="4:16" ht="15" thickBot="1"/>
+    <row r="30" spans="4:16">
+      <c r="E30" s="77" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="79"/>
+    </row>
+    <row r="31" spans="4:16" ht="15" thickBot="1">
+      <c r="E31" s="80"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="82"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1"/>
+    <row r="34" spans="1:7" ht="15" thickBot="1">
+      <c r="B34" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1">
+      <c r="B35" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="13">
-        <v>196875</v>
-      </c>
-      <c r="D4" s="13">
-        <v>749000</v>
-      </c>
-      <c r="E4" s="13">
-        <v>712250</v>
-      </c>
-      <c r="F4" s="14">
-        <v>673750</v>
-      </c>
-      <c r="G4" s="13">
-        <v>633063</v>
-      </c>
-      <c r="H4" s="14">
-        <v>697811</v>
-      </c>
-      <c r="I4" s="14">
-        <v>727562</v>
-      </c>
-      <c r="J4" s="15">
-        <f t="shared" si="0"/>
-        <v>4390311</v>
+      <c r="C35" s="23">
+        <v>2360000</v>
+      </c>
+      <c r="D35" s="24">
+        <v>1888000</v>
+      </c>
+      <c r="E35" s="24">
+        <v>1652000</v>
+      </c>
+      <c r="F35" s="24">
+        <v>1888000</v>
+      </c>
+      <c r="G35" s="24">
+        <v>7788000</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="70">
-      <c r="A5" s="9" t="s">
+    <row r="36" spans="1:7" ht="15" thickBot="1">
+      <c r="B36" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="23">
+        <v>500000</v>
+      </c>
+      <c r="D36" s="24">
+        <v>1200000</v>
+      </c>
+      <c r="E36" s="24">
+        <v>0</v>
+      </c>
+      <c r="F36" s="24">
+        <v>0</v>
+      </c>
+      <c r="G36" s="24">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1">
+      <c r="B37" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="13">
-        <v>196875</v>
-      </c>
-      <c r="D5" s="13">
-        <v>637000</v>
-      </c>
-      <c r="E5" s="13">
-        <v>780063</v>
-      </c>
-      <c r="F5" s="14">
-        <v>634813</v>
-      </c>
-      <c r="G5" s="13">
-        <v>604188</v>
-      </c>
-      <c r="H5" s="14">
-        <v>585375</v>
-      </c>
-      <c r="I5" s="14">
-        <v>605936</v>
-      </c>
-      <c r="J5" s="15">
-        <f t="shared" si="0"/>
-        <v>4044250</v>
+      <c r="C37" s="23">
+        <v>100000</v>
+      </c>
+      <c r="D37" s="24">
+        <v>400000</v>
+      </c>
+      <c r="E37" s="24">
+        <v>0</v>
+      </c>
+      <c r="F37" s="24">
+        <v>0</v>
+      </c>
+      <c r="G37" s="24">
+        <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="56">
-      <c r="A6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="13">
-        <v>177188</v>
-      </c>
-      <c r="D6" s="13">
-        <v>735875</v>
-      </c>
-      <c r="E6" s="16">
-        <v>787500</v>
-      </c>
-      <c r="F6" s="14">
-        <v>722750</v>
-      </c>
-      <c r="G6" s="13">
-        <v>644875</v>
-      </c>
-      <c r="H6" s="14">
-        <v>700437</v>
-      </c>
-      <c r="I6" s="14">
-        <v>688799</v>
-      </c>
-      <c r="J6" s="15">
-        <f t="shared" si="0"/>
-        <v>4457424</v>
+    <row r="40" spans="1:7" ht="20">
+      <c r="A40" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="70">
-      <c r="A7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="13">
-        <v>334469</v>
-      </c>
-      <c r="E7" s="16">
-        <v>787500</v>
-      </c>
-      <c r="F7" s="14">
-        <v>703850</v>
-      </c>
-      <c r="G7" s="13">
-        <v>615125</v>
-      </c>
-      <c r="H7" s="14">
-        <v>624751</v>
-      </c>
-      <c r="I7" s="14">
-        <v>636563</v>
-      </c>
-      <c r="J7" s="15">
-        <f t="shared" si="0"/>
-        <v>3702258</v>
+    <row r="41" spans="1:7" ht="20">
+      <c r="B41" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="55">
+        <v>7788000</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="11">
-        <v>902125</v>
-      </c>
-      <c r="D8" s="11">
-        <v>3620094</v>
-      </c>
-      <c r="E8" s="11">
-        <v>4334750</v>
-      </c>
-      <c r="F8" s="11">
-        <v>3868725</v>
-      </c>
-      <c r="G8" s="11">
-        <v>3554688</v>
-      </c>
-      <c r="H8" s="11">
-        <f>+SUM(H2:H7)</f>
-        <v>3767749</v>
-      </c>
-      <c r="I8" s="11">
-        <f>+SUM(I2:I7)</f>
-        <v>3648048</v>
-      </c>
-      <c r="J8" s="11">
-        <f t="shared" si="0"/>
-        <v>23696179</v>
+    <row r="42" spans="1:7" ht="20">
+      <c r="B42" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="53">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="20">
+      <c r="B43" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="53">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="20">
+      <c r="B44" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="54">
+        <f>+SUM(C41:C43)</f>
+        <v>9988000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A8:B8"/>
+  <mergeCells count="14">
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="E30:H31"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="M5:N5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="I24:J24" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="C1" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1">
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="82"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="42">
+      <c r="A4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="13">
+        <v>196875</v>
+      </c>
+      <c r="D4" s="13">
+        <v>645313</v>
+      </c>
+      <c r="E4" s="13">
+        <v>656250</v>
+      </c>
+      <c r="F4" s="14">
+        <v>581875</v>
+      </c>
+      <c r="G4" s="14">
+        <v>578813</v>
+      </c>
+      <c r="H4" s="14">
+        <v>580125</v>
+      </c>
+      <c r="I4" s="14">
+        <v>545125</v>
+      </c>
+      <c r="J4" s="15">
+        <f>+SUM(C4:I4)</f>
+        <v>3784376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="42">
+      <c r="A5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="13">
+        <v>134313</v>
+      </c>
+      <c r="D5" s="13">
+        <v>518438</v>
+      </c>
+      <c r="E5" s="13">
+        <v>611188</v>
+      </c>
+      <c r="F5" s="14">
+        <v>551688</v>
+      </c>
+      <c r="G5" s="13">
+        <v>478625</v>
+      </c>
+      <c r="H5" s="14">
+        <v>579250</v>
+      </c>
+      <c r="I5" s="14">
+        <v>444063</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" ref="J5:J10" si="0">+SUM(C5:I5)</f>
+        <v>3317565</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="42">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="13">
+        <v>196875</v>
+      </c>
+      <c r="D6" s="13">
+        <v>749000</v>
+      </c>
+      <c r="E6" s="13">
+        <v>712250</v>
+      </c>
+      <c r="F6" s="14">
+        <v>673750</v>
+      </c>
+      <c r="G6" s="13">
+        <v>633063</v>
+      </c>
+      <c r="H6" s="14">
+        <v>697811</v>
+      </c>
+      <c r="I6" s="14">
+        <v>727562</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="0"/>
+        <v>4390311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="70">
+      <c r="A7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="13">
+        <v>196875</v>
+      </c>
+      <c r="D7" s="13">
+        <v>637000</v>
+      </c>
+      <c r="E7" s="13">
+        <v>780063</v>
+      </c>
+      <c r="F7" s="14">
+        <v>634813</v>
+      </c>
+      <c r="G7" s="13">
+        <v>604188</v>
+      </c>
+      <c r="H7" s="14">
+        <v>585375</v>
+      </c>
+      <c r="I7" s="14">
+        <v>605936</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="0"/>
+        <v>4044250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="56">
+      <c r="A8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="13">
+        <v>177188</v>
+      </c>
+      <c r="D8" s="13">
+        <v>735875</v>
+      </c>
+      <c r="E8" s="16">
+        <v>787500</v>
+      </c>
+      <c r="F8" s="14">
+        <v>722750</v>
+      </c>
+      <c r="G8" s="13">
+        <v>644875</v>
+      </c>
+      <c r="H8" s="14">
+        <v>700437</v>
+      </c>
+      <c r="I8" s="14">
+        <v>688799</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="0"/>
+        <v>4457424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="70">
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="13">
+        <v>334469</v>
+      </c>
+      <c r="E9" s="16">
+        <v>787500</v>
+      </c>
+      <c r="F9" s="14">
+        <v>703850</v>
+      </c>
+      <c r="G9" s="13">
+        <v>615125</v>
+      </c>
+      <c r="H9" s="14">
+        <v>624751</v>
+      </c>
+      <c r="I9" s="14">
+        <v>636563</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="0"/>
+        <v>3702258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="76"/>
+      <c r="C10" s="11">
+        <v>902125</v>
+      </c>
+      <c r="D10" s="11">
+        <v>3620094</v>
+      </c>
+      <c r="E10" s="11">
+        <v>4334750</v>
+      </c>
+      <c r="F10" s="11">
+        <v>3868725</v>
+      </c>
+      <c r="G10" s="11">
+        <v>3554688</v>
+      </c>
+      <c r="H10" s="11">
+        <f>+SUM(H4:H9)</f>
+        <v>3767749</v>
+      </c>
+      <c r="I10" s="11">
+        <f>+SUM(I4:I9)</f>
+        <v>3648048</v>
+      </c>
+      <c r="J10" s="11">
+        <f t="shared" si="0"/>
+        <v>23696179</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C1:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>